--- a/output/2026-09-20_12_Croazia_Splitsko-dalmatinska_Cleaning.xlsx
+++ b/output/2026-09-20_12_Croazia_Splitsko-dalmatinska_Cleaning.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_12_Croazia_Splitsko-dalmatinska_Cleaning.xlsx
+++ b/output/2026-09-20_12_Croazia_Splitsko-dalmatinska_Cleaning.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rivenditore utensili professionali/industriali incl. aspiratori industriali (Makita, Bosch), assistenza e ricambi. Filiale Split confermata e operativa; confermata vendita aspiratori industriali tramite catalogo online</t>
+          <t>Rivenditore utensili professionali/industriali incl. aspiratori industriali (Makita, Bosch), assistenza e ricambi. Filiale Split confermata e operativa; confermata vendita aspiratori industriali tramite catalogo online [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
